--- a/Configs/Excel/CfgReward.xlsx
+++ b/Configs/Excel/CfgReward.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\DreamTileNew\Configs\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9518E1-2422-4E55-AB44-705499461655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FE62EF-3737-4F80-9F15-91F492AD5B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1389,13 +1389,7 @@
     <t>78;79;80;81;82;83;84;85;86;87</t>
   </si>
   <si>
-    <t>2236;2204;2205;2206;2207;2209;2210;2211;2212;2213</t>
-  </si>
-  <si>
     <t>88;89;90;91;92;93;94;95;96;97;98;99;100;101;102;103;104;105;106;107</t>
-  </si>
-  <si>
-    <t>2245;2214;2215;2216;2217;2218;2219;2220;2221;2222;2223;2224;2225;2226;2227;2228;2229;2230;2231;2232</t>
   </si>
   <si>
     <t>无尽宝藏循环组</t>
@@ -1448,12 +1442,20 @@
   <si>
     <t>2198;2201;2202;2204;2205;2206;2207;2209;2210;2211;2212;2213;2214;2215;2216;2217;2218;2219;2220;2221;2222;2223;2224;2225;2226;2227;2228;2229;2230;2231;2232;2233;2234;2235;2236;2245</t>
   </si>
+  <si>
+    <t>2215;2245;2214;2216;2217;2218;2219;2220;2221;2222;2223;2224;2225;2226;2227;2228;2229;2230;2231;2232</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2212;2205;2236;2204;2206;2207;2209;2210;2211;2213</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1503,6 +1505,13 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1556,7 +1565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1592,6 +1601,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1935,18 +1947,18 @@
       <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
@@ -2193,18 +2205,18 @@
       <c r="C2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -2773,7 +2785,7 @@
         <v>105</v>
       </c>
       <c r="F14" s="3">
-        <v>2198</v>
+        <v>2235</v>
       </c>
       <c r="G14" s="3">
         <v>1</v>
@@ -10092,8 +10104,8 @@
       <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>49</v>
+      <c r="D5" s="16" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -10101,92 +10113,92 @@
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B7" s="5">
         <v>4</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B8" s="5">
         <v>5</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3">
         <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="3">
         <v>7</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Excel/CfgReward.xlsx
+++ b/Configs/Excel/CfgReward.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\DreamTileNew\Configs\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FE62EF-3737-4F80-9F15-91F492AD5B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EEE72D-A5BE-496D-97A1-C29324849056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AllReward" sheetId="1" r:id="rId1"/>
@@ -1447,7 +1447,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>2212;2205;2236;2204;2206;2207;2209;2210;2211;2213</t>
+    <t>2236;2212;2205;2204;2206;2207;2209;2210;2211;2213</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -2808,7 +2808,7 @@
         <v>106</v>
       </c>
       <c r="F15" s="3">
-        <v>2233</v>
+        <v>2205</v>
       </c>
       <c r="G15" s="3">
         <v>1</v>
@@ -10227,6 +10227,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="2"/>
+  <pixelatorList sheetStid="3"/>
+</pixelators>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <commentList sheetStid="1">
     <commentChains s:ref="E3" rgbClr="FF0000">
@@ -11475,14 +11483,6 @@
 </comments>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="2"/>
-  <pixelatorList sheetStid="3"/>
-</pixelators>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
   <ds:schemaRefs>
@@ -11493,7 +11493,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A0048C-2381-489B-AA07-9611017176EA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
@@ -11502,7 +11502,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A0048C-2381-489B-AA07-9611017176EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
